--- a/grupos/6AEV - Estadisticos 20232.xlsx
+++ b/grupos/6AEV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="87">
   <si>
     <t>Materia</t>
   </si>
@@ -197,7 +197,7 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>CASTILLO</t>
+    <t>MORALES</t>
   </si>
   <si>
     <t>ROSAS</t>
@@ -218,16 +218,16 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>MIXCOA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>SORIA</t>
@@ -242,16 +242,16 @@
     <t>MORA</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
     <t>DE LA CRUZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MIGUEL</t>
   </si>
   <si>
     <t>JESUS EMMANUEL</t>
@@ -272,16 +272,13 @@
     <t>DULIAM</t>
   </si>
   <si>
-    <t>FELIX RAYMUNDO</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
-  </si>
-  <si>
     <t>OMAR</t>
   </si>
   <si>
-    <t>MIGUEL</t>
+    <t>JOSE EDUARDO</t>
+  </si>
+  <si>
+    <t>JAFET</t>
   </si>
 </sst>
 </file>
@@ -789,22 +786,22 @@
         <v>4</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -825,7 +822,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>7</v>
@@ -834,10 +831,10 @@
         <v>6</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -866,22 +863,22 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -905,10 +902,10 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W5">
         <v>7</v>
@@ -917,7 +914,7 @@
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -943,22 +940,22 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -982,13 +979,13 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V6">
         <v>8</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1020,22 +1017,22 @@
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1056,19 +1053,19 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1097,22 +1094,22 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1133,19 +1130,19 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>8</v>
       </c>
       <c r="X8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y8">
         <v>9</v>
@@ -1174,22 +1171,22 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1219,10 +1216,10 @@
         <v>8</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1251,22 +1248,22 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1290,13 +1287,13 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>7</v>
@@ -1328,22 +1325,22 @@
         <v>4</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1364,16 +1361,16 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U11">
         <v>5</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -1405,22 +1402,22 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1441,22 +1438,22 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V12">
         <v>8</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1482,22 +1479,22 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1521,19 +1518,19 @@
         <v>5</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V13">
         <v>7</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1559,22 +1556,22 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1598,16 +1595,16 @@
         <v>5</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>8</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1636,22 +1633,22 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1713,22 +1710,22 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1749,16 +1746,16 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>8</v>
@@ -1790,22 +1787,22 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1829,19 +1826,19 @@
         <v>8</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
         <v>8</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1867,22 +1864,22 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1903,22 +1900,22 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>7</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1944,22 +1941,22 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1980,10 +1977,10 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -2021,22 +2018,22 @@
         <v>4</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2057,13 +2054,13 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U20">
         <v>5</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2098,22 +2095,22 @@
         <v>4</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2134,13 +2131,13 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U21">
         <v>5</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2175,22 +2172,22 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2211,7 +2208,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>9</v>
@@ -2220,7 +2217,7 @@
         <v>8</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2252,22 +2249,22 @@
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2288,7 +2285,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>10</v>
@@ -2297,13 +2294,13 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>6</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2329,22 +2326,22 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2365,13 +2362,13 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>5</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2406,22 +2403,22 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2445,10 +2442,10 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W25">
         <v>7</v>
@@ -2457,7 +2454,7 @@
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2483,22 +2480,22 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2522,13 +2519,13 @@
         <v>5</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>8</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>5</v>
@@ -2560,22 +2557,22 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2599,13 +2596,13 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>8</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -2637,22 +2634,22 @@
         <v>6</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2673,16 +2670,16 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V28">
         <v>8</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -2714,22 +2711,22 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2750,10 +2747,10 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>8</v>
@@ -2907,16 +2904,16 @@
         <v>100</v>
       </c>
       <c r="J4">
-        <v>94.7</v>
+        <v>95.2</v>
       </c>
       <c r="K4">
-        <v>94.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="L4">
-        <v>93.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M4">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N4">
         <v>100</v>
@@ -2925,16 +2922,16 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>94.7</v>
+        <v>95.2</v>
       </c>
       <c r="Q4">
-        <v>94.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="R4">
-        <v>93.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S4">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2966,16 +2963,16 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>89.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K5">
-        <v>94.7</v>
+        <v>93.7</v>
       </c>
       <c r="L5">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M5">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N5">
         <v>100</v>
@@ -2984,16 +2981,16 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>89.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Q5">
-        <v>94.7</v>
+        <v>93.7</v>
       </c>
       <c r="R5">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S5">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3025,13 +3022,13 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>89.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K6">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="M6">
         <v>100</v>
@@ -3043,13 +3040,13 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>89.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Q6">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="R6">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -3084,13 +3081,13 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -3102,13 +3099,13 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q7">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R7">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -3143,13 +3140,13 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K8">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="L8">
-        <v>93.3</v>
+        <v>87.3</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -3161,13 +3158,13 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q8">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="R8">
-        <v>93.3</v>
+        <v>87.3</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -3205,10 +3202,10 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="L9">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -3223,10 +3220,10 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>94.7</v>
+        <v>97.5</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -3261,13 +3258,13 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>89.5</v>
+        <v>90.5</v>
       </c>
       <c r="K10">
-        <v>89.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L10">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -3279,13 +3276,13 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>89.5</v>
+        <v>90.5</v>
       </c>
       <c r="Q10">
-        <v>89.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="R10">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3320,16 +3317,16 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="K11">
-        <v>81.59999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L11">
-        <v>96.7</v>
+        <v>87.3</v>
       </c>
       <c r="M11">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="N11">
         <v>100</v>
@@ -3338,16 +3335,16 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="Q11">
-        <v>81.59999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="R11">
-        <v>96.7</v>
+        <v>87.3</v>
       </c>
       <c r="S11">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3379,13 +3376,13 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>94.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K12">
-        <v>86.8</v>
+        <v>93.7</v>
       </c>
       <c r="L12">
-        <v>93.3</v>
+        <v>94.5</v>
       </c>
       <c r="M12">
         <v>100</v>
@@ -3397,13 +3394,13 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>94.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q12">
-        <v>86.8</v>
+        <v>93.7</v>
       </c>
       <c r="R12">
-        <v>93.3</v>
+        <v>94.5</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -3438,13 +3435,13 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>84.2</v>
+        <v>85.7</v>
       </c>
       <c r="K13">
-        <v>89.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="L13">
-        <v>90</v>
+        <v>85.5</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -3456,13 +3453,13 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>84.2</v>
+        <v>85.7</v>
       </c>
       <c r="Q13">
-        <v>89.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="R13">
-        <v>90</v>
+        <v>85.5</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -3497,13 +3494,13 @@
         <v>100</v>
       </c>
       <c r="J14">
-        <v>84.2</v>
+        <v>85.7</v>
       </c>
       <c r="K14">
-        <v>92.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="L14">
-        <v>83.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -3515,13 +3512,13 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>84.2</v>
+        <v>85.7</v>
       </c>
       <c r="Q14">
-        <v>92.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="R14">
-        <v>83.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -3562,7 +3559,7 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -3580,7 +3577,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -3615,13 +3612,13 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>94.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K16">
-        <v>92.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="L16">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -3633,13 +3630,13 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>94.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q16">
-        <v>92.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="R16">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -3674,13 +3671,13 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>89.5</v>
+        <v>90.5</v>
       </c>
       <c r="K17">
-        <v>92.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="L17">
-        <v>90</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -3692,13 +3689,13 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>89.5</v>
+        <v>90.5</v>
       </c>
       <c r="Q17">
-        <v>92.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="R17">
-        <v>90</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -3733,13 +3730,13 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>84.2</v>
+        <v>90.5</v>
       </c>
       <c r="K18">
-        <v>92.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="L18">
-        <v>96.7</v>
+        <v>92.7</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -3751,13 +3748,13 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>84.2</v>
+        <v>90.5</v>
       </c>
       <c r="Q18">
-        <v>92.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="R18">
-        <v>96.7</v>
+        <v>92.7</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -3792,13 +3789,13 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>94.7</v>
+        <v>90.5</v>
       </c>
       <c r="K19">
-        <v>92.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="L19">
-        <v>86.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -3810,13 +3807,13 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>94.7</v>
+        <v>90.5</v>
       </c>
       <c r="Q19">
-        <v>92.09999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="R19">
-        <v>86.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -3851,13 +3848,13 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>89.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K20">
-        <v>86.8</v>
+        <v>79.7</v>
       </c>
       <c r="L20">
-        <v>86.7</v>
+        <v>80</v>
       </c>
       <c r="M20">
         <v>72</v>
@@ -3869,13 +3866,13 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>89.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Q20">
-        <v>86.8</v>
+        <v>79.7</v>
       </c>
       <c r="R20">
-        <v>86.7</v>
+        <v>80</v>
       </c>
       <c r="S20">
         <v>72</v>
@@ -3910,13 +3907,13 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>89.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K21">
-        <v>89.5</v>
+        <v>83.5</v>
       </c>
       <c r="L21">
-        <v>90</v>
+        <v>81.8</v>
       </c>
       <c r="M21">
         <v>72</v>
@@ -3928,13 +3925,13 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>89.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Q21">
-        <v>89.5</v>
+        <v>83.5</v>
       </c>
       <c r="R21">
-        <v>90</v>
+        <v>81.8</v>
       </c>
       <c r="S21">
         <v>72</v>
@@ -3972,10 +3969,10 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>98.7</v>
       </c>
       <c r="L22">
-        <v>96.7</v>
+        <v>92.7</v>
       </c>
       <c r="M22">
         <v>100</v>
@@ -3990,10 +3987,10 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>98.7</v>
       </c>
       <c r="R22">
-        <v>96.7</v>
+        <v>92.7</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -4087,13 +4084,13 @@
         <v>100</v>
       </c>
       <c r="J24">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="K24">
-        <v>84.2</v>
+        <v>87.3</v>
       </c>
       <c r="L24">
-        <v>83.3</v>
+        <v>87.3</v>
       </c>
       <c r="M24">
         <v>100</v>
@@ -4105,13 +4102,13 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="Q24">
-        <v>84.2</v>
+        <v>87.3</v>
       </c>
       <c r="R24">
-        <v>83.3</v>
+        <v>87.3</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -4146,13 +4143,13 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>84.2</v>
+        <v>85.7</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="L25">
-        <v>90</v>
+        <v>87.3</v>
       </c>
       <c r="M25">
         <v>100</v>
@@ -4164,13 +4161,13 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>84.2</v>
+        <v>85.7</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="R25">
-        <v>90</v>
+        <v>87.3</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -4205,13 +4202,13 @@
         <v>100</v>
       </c>
       <c r="J26">
-        <v>89.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="K26">
-        <v>89.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="L26">
-        <v>86.7</v>
+        <v>92.7</v>
       </c>
       <c r="M26">
         <v>100</v>
@@ -4223,13 +4220,13 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>89.5</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="Q26">
-        <v>89.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="R26">
-        <v>86.7</v>
+        <v>92.7</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -4264,13 +4261,13 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>94.7</v>
+        <v>95.2</v>
       </c>
       <c r="K27">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="L27">
-        <v>96.7</v>
+        <v>92.7</v>
       </c>
       <c r="M27">
         <v>100</v>
@@ -4282,13 +4279,13 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>94.7</v>
+        <v>95.2</v>
       </c>
       <c r="Q27">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="R27">
-        <v>96.7</v>
+        <v>92.7</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -4323,13 +4320,13 @@
         <v>100</v>
       </c>
       <c r="J28">
-        <v>89.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K28">
-        <v>97.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="M28">
         <v>100</v>
@@ -4341,13 +4338,13 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>89.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="Q28">
-        <v>97.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="R28">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -4382,13 +4379,13 @@
         <v>100</v>
       </c>
       <c r="J29">
-        <v>94.7</v>
+        <v>90.5</v>
       </c>
       <c r="K29">
-        <v>92.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="L29">
-        <v>96.7</v>
+        <v>92.7</v>
       </c>
       <c r="M29">
         <v>100</v>
@@ -4400,13 +4397,13 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>94.7</v>
+        <v>90.5</v>
       </c>
       <c r="Q29">
-        <v>92.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="R29">
-        <v>96.7</v>
+        <v>92.7</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -4475,16 +4472,16 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>65.40000000000001</v>
+        <v>53.8</v>
       </c>
       <c r="G2" s="2">
-        <v>34.6</v>
+        <v>46.2</v>
       </c>
       <c r="H2">
         <v>6.1</v>
@@ -4507,19 +4504,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>69.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>30.8</v>
+        <v>26.9</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4539,19 +4536,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>76.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G4" s="2">
-        <v>23.1</v>
+        <v>26.9</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4571,19 +4568,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>84.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="G5" s="2">
-        <v>15.4</v>
+        <v>19.2</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4594,7 +4591,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
@@ -4615,7 +4612,7 @@
         <v>3.8</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4626,7 +4623,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>54</v>
@@ -4647,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4697,7 +4694,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4729,7 +4726,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920005</v>
+        <v>21330051920379</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
@@ -4741,10 +4738,10 @@
         <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4752,7 +4749,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920005</v>
+        <v>21330051920379</v>
       </c>
       <c r="B3" t="s">
         <v>59</v>
@@ -4948,10 +4945,10 @@
         <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4982,7 +4979,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920160</v>
+        <v>21330051920013</v>
       </c>
       <c r="B13" t="s">
         <v>66</v>
@@ -5005,22 +5002,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920012</v>
+        <v>20330051920022</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
         <v>85</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5028,47 +5025,24 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>21330051920013</v>
+        <v>21330051920028</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
         <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920379</v>
-      </c>
-      <c r="B16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" t="s">
-        <v>76</v>
-      </c>
-      <c r="D16" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6AEV - Estadisticos 20232.xlsx
+++ b/grupos/6AEV - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="68">
   <si>
     <t>Materia</t>
   </si>
@@ -179,12 +179,12 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Silva Villegas Mario</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Silva Villegas Mario</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -197,88 +197,31 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>MORALES</t>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
   </si>
   <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MIXCOA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>SORIA</t>
   </si>
   <si>
-    <t>ATENOGENES</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MIGUEL</t>
+    <t>DULIAM</t>
+  </si>
+  <si>
+    <t>ELI ANTONIO</t>
+  </si>
+  <si>
+    <t>ISAAC</t>
   </si>
   <si>
     <t>JESUS EMMANUEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO</t>
-  </si>
-  <si>
-    <t>JOSE DAMIAN</t>
-  </si>
-  <si>
-    <t>DULIAM</t>
-  </si>
-  <si>
-    <t>OMAR</t>
-  </si>
-  <si>
-    <t>JOSE EDUARDO</t>
-  </si>
-  <si>
-    <t>JAFET</t>
   </si>
 </sst>
 </file>
@@ -804,31 +747,31 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
         <v>7</v>
       </c>
       <c r="U4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -837,7 +780,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -881,40 +824,40 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>7</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -958,22 +901,22 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -988,10 +931,10 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1035,28 +978,28 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>9</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1112,28 +1055,28 @@
         <v>8</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1142,10 +1085,10 @@
         <v>8</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1189,37 +1132,37 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>9</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1266,28 +1209,28 @@
         <v>7</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
         <v>5</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>8</v>
@@ -1343,40 +1286,40 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>7</v>
       </c>
       <c r="W11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1420,22 +1363,22 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>6</v>
@@ -1450,7 +1393,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1497,28 +1440,28 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1527,7 +1470,7 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>7</v>
@@ -1574,40 +1517,40 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V14">
         <v>8</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1651,22 +1594,22 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1675,13 +1618,13 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>9</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>9</v>
@@ -1728,37 +1671,37 @@
         <v>8</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>8</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1805,22 +1748,22 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -1835,7 +1778,7 @@
         <v>9</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -1882,40 +1825,40 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <v>7</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>7</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1959,28 +1902,28 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T19">
         <v>7</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>8</v>
@@ -1989,7 +1932,7 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2036,28 +1979,28 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2069,7 +2012,7 @@
         <v>5</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2113,28 +2056,28 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>7</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V21">
         <v>6</v>
@@ -2146,7 +2089,7 @@
         <v>5</v>
       </c>
       <c r="Y21">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2190,22 +2133,22 @@
         <v>8</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>7</v>
@@ -2267,22 +2210,22 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2344,28 +2287,28 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>6</v>
@@ -2421,40 +2364,40 @@
         <v>8</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U25">
         <v>8</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>7</v>
       </c>
       <c r="X25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2498,28 +2441,28 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2528,7 +2471,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -2575,31 +2518,31 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -2652,37 +2595,37 @@
         <v>6</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
         <v>6</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>7</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>6</v>
@@ -2729,22 +2672,22 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>7</v>
@@ -2922,16 +2865,16 @@
         <v>100</v>
       </c>
       <c r="P4">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="Q4">
-        <v>94.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R4">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="S4">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2981,16 +2924,16 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>88.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q5">
-        <v>93.7</v>
+        <v>94.8</v>
       </c>
       <c r="R5">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S5">
-        <v>74</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3040,13 +2983,13 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>88.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="Q6">
-        <v>97.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="R6">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -3099,13 +3042,13 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>92.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="Q7">
-        <v>97.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="R7">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -3158,13 +3101,13 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q8">
-        <v>97.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="R8">
-        <v>87.3</v>
+        <v>91.3</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -3217,13 +3160,13 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q9">
+        <v>100</v>
+      </c>
+      <c r="R9">
         <v>97.5</v>
-      </c>
-      <c r="R9">
-        <v>96.40000000000001</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -3276,13 +3219,13 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>90.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q10">
-        <v>92.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="R10">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3335,16 +3278,16 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>95.2</v>
+        <v>93.5</v>
       </c>
       <c r="Q11">
-        <v>88.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R11">
-        <v>87.3</v>
+        <v>91.3</v>
       </c>
       <c r="S11">
-        <v>86</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3394,13 +3337,13 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>92.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="Q12">
-        <v>93.7</v>
+        <v>95.7</v>
       </c>
       <c r="R12">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -3453,13 +3396,13 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>85.7</v>
+        <v>90.3</v>
       </c>
       <c r="Q13">
-        <v>92.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="R13">
-        <v>85.5</v>
+        <v>90</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -3512,13 +3455,13 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>85.7</v>
+        <v>88.7</v>
       </c>
       <c r="Q14">
-        <v>93.7</v>
+        <v>94.8</v>
       </c>
       <c r="R14">
-        <v>89.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -3577,7 +3520,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -3630,13 +3573,13 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>92.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="Q16">
-        <v>93.7</v>
+        <v>95.7</v>
       </c>
       <c r="R16">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -3689,13 +3632,13 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>90.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q17">
-        <v>96.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="R17">
-        <v>89.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -3748,13 +3691,13 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>90.5</v>
+        <v>90.3</v>
       </c>
       <c r="Q18">
-        <v>93.7</v>
+        <v>94</v>
       </c>
       <c r="R18">
-        <v>92.7</v>
+        <v>95</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -3807,13 +3750,13 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>90.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q19">
-        <v>93.7</v>
+        <v>94</v>
       </c>
       <c r="R19">
-        <v>89.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -3866,16 +3809,16 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>88.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q20">
-        <v>79.7</v>
+        <v>88.8</v>
       </c>
       <c r="R20">
-        <v>80</v>
+        <v>86.3</v>
       </c>
       <c r="S20">
-        <v>72</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3925,16 +3868,16 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>88.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="Q21">
-        <v>83.5</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="R21">
-        <v>81.8</v>
+        <v>87.5</v>
       </c>
       <c r="S21">
-        <v>72</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -3987,10 +3930,10 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>98.7</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="R22">
-        <v>92.7</v>
+        <v>95</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -4102,13 +4045,13 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>97.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="Q24">
-        <v>87.3</v>
+        <v>94</v>
       </c>
       <c r="R24">
-        <v>87.3</v>
+        <v>91.3</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -4161,13 +4104,13 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>85.7</v>
+        <v>88.7</v>
       </c>
       <c r="Q25">
-        <v>94.90000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="R25">
-        <v>87.3</v>
+        <v>91.3</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -4220,13 +4163,13 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>88.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q26">
-        <v>94.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R26">
-        <v>92.7</v>
+        <v>95</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -4279,13 +4222,13 @@
         <v>100</v>
       </c>
       <c r="P27">
-        <v>95.2</v>
+        <v>96.8</v>
       </c>
       <c r="Q27">
-        <v>97.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="R27">
-        <v>92.7</v>
+        <v>95</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -4338,13 +4281,13 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>92.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="Q28">
-        <v>96.2</v>
+        <v>98.3</v>
       </c>
       <c r="R28">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
       <c r="S28">
         <v>100</v>
@@ -4397,13 +4340,13 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>90.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="Q29">
-        <v>96.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="R29">
-        <v>92.7</v>
+        <v>95</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -4472,19 +4415,19 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2">
-        <v>53.8</v>
+        <v>88.5</v>
       </c>
       <c r="G2" s="2">
-        <v>46.2</v>
+        <v>11.5</v>
       </c>
       <c r="H2">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4504,19 +4447,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>73.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="G3" s="2">
-        <v>26.9</v>
+        <v>3.8</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4536,19 +4479,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>73.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>26.9</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4559,7 +4502,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
@@ -4568,19 +4511,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>80.8</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4591,28 +4534,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6">
         <v>26</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4623,7 +4566,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>54</v>
@@ -4644,7 +4587,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4694,7 +4637,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4726,22 +4669,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920379</v>
+        <v>20330051920078</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4749,16 +4692,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920379</v>
+        <v>20330051920366</v>
       </c>
       <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
         <v>59</v>
       </c>
-      <c r="C3" t="s">
-        <v>69</v>
-      </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -4772,22 +4715,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920021</v>
+        <v>20330051920367</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4798,13 +4741,13 @@
         <v>21330051920021</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -4813,236 +4756,6 @@
         <v>50</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920022</v>
-      </c>
-      <c r="B6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920022</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>79</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920023</v>
-      </c>
-      <c r="B8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920023</v>
-      </c>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920003</v>
-      </c>
-      <c r="B10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920010</v>
-      </c>
-      <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920078</v>
-      </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920013</v>
-      </c>
-      <c r="B13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" t="s">
-        <v>84</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920022</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" t="s">
-        <v>85</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920028</v>
-      </c>
-      <c r="B15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>
